--- a/view/viewList_protocolCore.xlsx
+++ b/view/viewList_protocolCore.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3205067-DB87-4BBA-AF61-0A4362AFB05F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Viste" sheetId="1" r:id="rId1"/>

--- a/view/viewList_protocolCore.xlsx
+++ b/view/viewList_protocolCore.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mcorbara\Documents\ArgoX3_API_Mobile_CORE\view\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3205067-DB87-4BBA-AF61-0A4362AFB05F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3800671D-2439-42B8-8857-802D9AF51BD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23280" yWindow="2715" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Viste" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="54">
   <si>
     <t>Codice Vista</t>
   </si>
@@ -158,6 +158,39 @@
   </si>
   <si>
     <t>Dim</t>
+  </si>
+  <si>
+    <t>Gestione protocollo Funzione  AX3M</t>
+  </si>
+  <si>
+    <t>Gestione menù funzioni (ad albero)</t>
+  </si>
+  <si>
+    <t>YVCONTROLLER</t>
+  </si>
+  <si>
+    <t>YVCNTRL</t>
+  </si>
+  <si>
+    <t>Vista Controllers (menùAlbero)</t>
+  </si>
+  <si>
+    <t>YVPFCONTR</t>
+  </si>
+  <si>
+    <t>YVPFCONT</t>
+  </si>
+  <si>
+    <t>Controller Profilo Funzione</t>
+  </si>
+  <si>
+    <t>Codice Tipo per Patch</t>
+  </si>
+  <si>
+    <t>Note per Patch</t>
+  </si>
+  <si>
+    <t>AVW</t>
   </si>
 </sst>
 </file>
@@ -181,15 +214,21 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="13">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -335,11 +374,110 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -398,6 +536,61 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -678,7 +871,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34.5703125" customWidth="1"/>
@@ -686,50 +879,67 @@
     <col min="3" max="3" width="35" customWidth="1"/>
     <col min="5" max="5" width="17.42578125" customWidth="1"/>
     <col min="6" max="6" width="22.42578125" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="21.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:8" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="33" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+      <c r="G1" s="32" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1" s="32" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="30" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="8" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="G3" s="35" t="s">
+        <v>53</v>
+      </c>
+      <c r="H3" s="37"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="13" t="s">
         <v>12</v>
       </c>
       <c r="B4" s="6" t="s">
@@ -744,12 +954,16 @@
       <c r="E4" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="9" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
+      <c r="G4" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H4" s="38"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
         <v>13</v>
       </c>
       <c r="B5" s="6" t="s">
@@ -764,12 +978,16 @@
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="9" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+      <c r="G5" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H5" s="38"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
         <v>7</v>
       </c>
       <c r="B6" s="6" t="s">
@@ -784,12 +1002,16 @@
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="9" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
+      <c r="G6" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H6" s="38"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="13" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="6" t="s">
@@ -804,12 +1026,16 @@
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="9" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
+      <c r="G7" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H7" s="38"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
         <v>15</v>
       </c>
       <c r="B8" s="6" t="s">
@@ -824,9 +1050,98 @@
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="9" t="s">
         <v>22</v>
       </c>
+      <c r="G8" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H8" s="38"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="25"/>
+      <c r="F9" s="27"/>
+      <c r="G9" s="34"/>
+      <c r="H9" s="38"/>
+    </row>
+    <row r="10" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="26"/>
+      <c r="B10" s="28"/>
+      <c r="C10" s="28"/>
+      <c r="D10" s="28"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="36"/>
+      <c r="H10" s="39"/>
+    </row>
+    <row r="11" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G11" s="34"/>
+      <c r="H11" s="34"/>
+    </row>
+    <row r="12" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="G12" s="34"/>
+      <c r="H12" s="34"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G13" s="43" t="s">
+        <v>53</v>
+      </c>
+      <c r="H13" s="40"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G14" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="H14" s="41"/>
+    </row>
+    <row r="15" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="14"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="29"/>
+      <c r="H15" s="42"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -835,25 +1150,29 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87960965-DC7A-452D-9138-227F9365F5E9}">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.5703125" customWidth="1"/>
-    <col min="2" max="2" width="35.7109375" customWidth="1"/>
+    <col min="1" max="1" width="42" customWidth="1"/>
+    <col min="2" max="2" width="38.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="31" t="s">
         <v>32</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="30" t="s">
+        <v>43</v>
+      </c>
+    </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
         <v>16</v>
@@ -960,6 +1279,43 @@
         <v>8</v>
       </c>
       <c r="C15" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="30" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="B20" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="14"/>
+      <c r="B21" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="11" t="s">
         <v>8</v>
       </c>
     </row>
